--- a/assets/BOs/Amaterasu.xlsx
+++ b/assets/BOs/Amaterasu.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\OneDrive\Github\DoD\DeitiesOfDeath\public\assets\BOs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\doc\coding\DoD\DeitiesOfDeath\public\assets\BOs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6708109-4FCA-4A47-A4AF-EE9457F8FB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD77455-3E7F-43F3-9150-D1864F5E390F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9930" yWindow="4395" windowWidth="43200" windowHeight="23445" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="88">
   <si>
-    <t>Amaterasu 2 Shrine Classical Fight - By ikosaeder</t>
-  </si>
-  <si>
     <t>Archaic</t>
   </si>
   <si>
@@ -359,9 +356,6 @@
     <t>7 to Gold (start gold)</t>
   </si>
   <si>
-    <t>Amaterasu 2 Shrine 2nd TC - By ikosaeder</t>
-  </si>
-  <si>
     <t>Miko builds Shrine at Wood (*forest next to Gold* to affect gold mine) and prays.
 In Shrine: Pre-Queue Kagura tech.
 Don't send Herdables to Shrine for extra fattening (bugged atm), wait until they reach max capacity and then move them close.</t>
@@ -728,9 +722,6 @@
     <t>Use your god power at 2nd Town Center. Deer and Wolf spawn every 50 sec (max 10).</t>
   </si>
   <si>
-    <t>Amaterasu - Standard opening - TheRapl</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">3 </t>
     </r>
@@ -970,6 +961,15 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=Wo1Qb4GjJyI</t>
+  </si>
+  <si>
+    <t>Standard opening - TheRapl</t>
+  </si>
+  <si>
+    <t>2 Shrine 2nd TC - By ikosaeder</t>
+  </si>
+  <si>
+    <t>2 Shrine Classical Fight - By ikosaeder</t>
   </si>
 </sst>
 </file>
@@ -1186,6 +1186,21 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1201,21 +1216,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1236,7 +1236,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{704E7ECB-C4E5-41F8-9F4D-FE72C3664052}"/>
   </cellStyles>
@@ -1517,163 +1517,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="57.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="57.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="213.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="213.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="3" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="3" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="C17" s="1"/>
     </row>
@@ -1691,190 +1691,190 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D140E5-774D-4359-B785-6B9C8DDAAC82}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="119.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="223.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="119.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="223.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
       <c r="C4" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="B7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="B9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="B11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="C13" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="6" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="6" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1891,191 +1891,191 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95570D34-3036-488E-9B50-98F5BF6B06A9}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
       <c r="D1" s="19"/>
     </row>
-    <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
       <c r="D2" s="22"/>
     </row>
-    <row r="3" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-    </row>
-    <row r="4" spans="1:4" ht="101.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+    <row r="3" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+    </row>
+    <row r="4" spans="1:4" ht="97.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="12" t="s">
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:4" ht="97.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+      <c r="B6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+    </row>
+    <row r="7" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-    </row>
-    <row r="6" spans="1:4" ht="101.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="B7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="D7" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-    </row>
-    <row r="7" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="B8" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="C8" s="7" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="D8" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="12" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="20" t="s">
         <v>70</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
-        <v>73</v>
       </c>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
       <c r="D9" s="22"/>
     </row>
-    <row r="10" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-    </row>
-    <row r="11" spans="1:4" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+    <row r="10" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:4" ht="111.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="12" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="20" t="s">
         <v>75</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
-        <v>78</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
       <c r="D12" s="22"/>
     </row>
-    <row r="13" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-    </row>
-    <row r="14" spans="1:4" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+    <row r="13" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:4" ht="28.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="C15" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-    </row>
-    <row r="15" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+      <c r="D15" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="12" t="s">
+    </row>
+    <row r="16" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8"/>
+      <c r="B16" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+    </row>
+    <row r="19" spans="1:4" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-    </row>
-    <row r="19" spans="1:4" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
